--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486807_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486807_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.209199999999999</v>
+        <v>8.755599999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>7.7415</v>
+        <v>7.2382</v>
       </c>
       <c r="F2" t="n">
-        <v>1.4677</v>
+        <v>1.5174</v>
       </c>
       <c r="G2" t="n">
         <v>4.7462</v>
@@ -610,13 +610,13 @@
         <v>1.5446</v>
       </c>
       <c r="S2" t="n">
-        <v>2.019</v>
+        <v>1.5654</v>
       </c>
       <c r="T2" t="n">
-        <v>1.682</v>
+        <v>1.1788</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3369</v>
+        <v>0.3866</v>
       </c>
       <c r="V2" t="n">
         <v>0.8995</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.6834</v>
+        <v>5.0791</v>
       </c>
       <c r="E3" t="n">
-        <v>2.1287</v>
+        <v>3.1768</v>
       </c>
       <c r="F3" t="n">
-        <v>1.5546</v>
+        <v>1.9023</v>
       </c>
       <c r="G3" t="n">
         <v>2.9908</v>
@@ -688,13 +688,13 @@
         <v>1.5446</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.4578</v>
+        <v>0.9379</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.4416</v>
+        <v>0.6065</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0163</v>
+        <v>0.3314</v>
       </c>
       <c r="V3" t="n">
         <v>0.5712</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. AMON BYSTROVA</t>
+          <t>F. DIAZ MARTINEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.1605</v>
+        <v>3.4257</v>
       </c>
       <c r="E4" t="n">
-        <v>2.2757</v>
+        <v>2.5168</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8848</v>
+        <v>0.9089</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.3963</v>
+        <v>1.4533</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.351</v>
+        <v>-2.1027</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.0453</v>
+        <v>3.556</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0254</v>
+        <v>2.9999</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.178</v>
+        <v>-0.7914</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2035</v>
+        <v>3.7912</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.4217</v>
+        <v>-1.5465</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.173</v>
+        <v>-1.3113</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.2487</v>
+        <v>-0.2352</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.5446</v>
+        <v>-0.7723</v>
       </c>
       <c r="Q4" t="n">
         <v>-2.8962</v>
       </c>
       <c r="R4" t="n">
-        <v>1.3515</v>
+        <v>2.1239</v>
       </c>
       <c r="S4" t="n">
-        <v>5.202</v>
+        <v>2.1308</v>
       </c>
       <c r="T4" t="n">
-        <v>4.247</v>
+        <v>1.7992</v>
       </c>
       <c r="U4" t="n">
-        <v>0.9549</v>
+        <v>0.3316</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8995</v>
+        <v>0.6138</v>
       </c>
       <c r="W4" t="n">
-        <v>0.8995</v>
+        <v>0.6138</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>F. DIAZ MARTINEZ</t>
+          <t>J. SCHILB</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.1375</v>
+        <v>3.1119</v>
       </c>
       <c r="E5" t="n">
-        <v>1.9306</v>
+        <v>2.071</v>
       </c>
       <c r="F5" t="n">
-        <v>1.2069</v>
+        <v>1.0409</v>
       </c>
       <c r="G5" t="n">
-        <v>1.4533</v>
+        <v>2.9257</v>
       </c>
       <c r="H5" t="n">
-        <v>-2.1027</v>
+        <v>-0.5309</v>
       </c>
       <c r="I5" t="n">
-        <v>3.556</v>
+        <v>3.4565</v>
       </c>
       <c r="J5" t="n">
-        <v>2.9999</v>
+        <v>2.8503</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.7914</v>
+        <v>-0.3237</v>
       </c>
       <c r="L5" t="n">
-        <v>3.7912</v>
+        <v>3.174</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.5465</v>
+        <v>0.07530000000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.3113</v>
+        <v>-0.2072</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.2352</v>
+        <v>0.2826</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.7723</v>
+        <v>-1.1585</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.8962</v>
+        <v>-1.9308</v>
       </c>
       <c r="R5" t="n">
-        <v>2.1239</v>
+        <v>0.7723</v>
       </c>
       <c r="S5" t="n">
-        <v>1.8426</v>
+        <v>1.3447</v>
       </c>
       <c r="T5" t="n">
-        <v>1.2131</v>
+        <v>1.1514</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6296</v>
+        <v>0.1933</v>
       </c>
       <c r="V5" t="n">
-        <v>0.6138</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0.6138</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. SCHILB</t>
+          <t>D. SANCHEZ PEREZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.9588</v>
+        <v>1.8699</v>
       </c>
       <c r="E6" t="n">
-        <v>1.9675</v>
+        <v>-0.1442</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9912</v>
+        <v>2.0141</v>
       </c>
       <c r="G6" t="n">
-        <v>2.9257</v>
+        <v>-2.2621</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5309</v>
+        <v>-1.3036</v>
       </c>
       <c r="I6" t="n">
-        <v>3.4565</v>
+        <v>-0.9585</v>
       </c>
       <c r="J6" t="n">
-        <v>2.8503</v>
+        <v>-1.4541</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.3237</v>
+        <v>-0.1995</v>
       </c>
       <c r="L6" t="n">
-        <v>3.174</v>
+        <v>-1.2546</v>
       </c>
       <c r="M6" t="n">
-        <v>0.07530000000000001</v>
+        <v>-0.8080000000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.2072</v>
+        <v>-1.1041</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2826</v>
+        <v>0.2961</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.1585</v>
+        <v>0.7723</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.9308</v>
+        <v>-0.9654</v>
       </c>
       <c r="R6" t="n">
-        <v>0.7723</v>
+        <v>1.7377</v>
       </c>
       <c r="S6" t="n">
-        <v>1.1916</v>
+        <v>2.0894</v>
       </c>
       <c r="T6" t="n">
-        <v>1.048</v>
+        <v>1.6615</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1436</v>
+        <v>0.428</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.2703</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.6138</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>0.6565</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. SANCHEZ PEREZ</t>
+          <t>M. SOLA IDRISU</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.7721</v>
+        <v>0.8695000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.5648</v>
+        <v>-0.9361</v>
       </c>
       <c r="F7" t="n">
-        <v>2.3369</v>
+        <v>1.8055</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.2621</v>
+        <v>4.0731</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.3036</v>
+        <v>1.3241</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.9585</v>
+        <v>2.749</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.4541</v>
+        <v>4.585</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.1995</v>
+        <v>1.3251</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.2546</v>
+        <v>3.26</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.8080000000000001</v>
+        <v>-0.5119</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.1041</v>
+        <v>-0.0009</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2961</v>
+        <v>-0.511</v>
       </c>
       <c r="P7" t="n">
-        <v>0.7723</v>
+        <v>-4.6339</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9654</v>
+        <v>-6.7577</v>
       </c>
       <c r="R7" t="n">
-        <v>1.7377</v>
+        <v>2.1239</v>
       </c>
       <c r="S7" t="n">
-        <v>1.9916</v>
+        <v>1.7585</v>
       </c>
       <c r="T7" t="n">
-        <v>1.2408</v>
+        <v>1.5649</v>
       </c>
       <c r="U7" t="n">
-        <v>0.7508</v>
+        <v>0.1936</v>
       </c>
       <c r="V7" t="n">
-        <v>1.2703</v>
+        <v>-0.3282</v>
       </c>
       <c r="W7" t="n">
-        <v>0.6138</v>
+        <v>-0.3282</v>
       </c>
       <c r="X7" t="n">
-        <v>0.6565</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. SOLA IDRISU</t>
+          <t>G. PEREZ HERNANDEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9645</v>
+        <v>0.7731</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.7914</v>
+        <v>1.2496</v>
       </c>
       <c r="F8" t="n">
-        <v>1.7559</v>
+        <v>-0.4765</v>
       </c>
       <c r="G8" t="n">
-        <v>4.0731</v>
+        <v>1.904</v>
       </c>
       <c r="H8" t="n">
-        <v>1.3241</v>
+        <v>0.3034</v>
       </c>
       <c r="I8" t="n">
-        <v>2.749</v>
+        <v>1.6005</v>
       </c>
       <c r="J8" t="n">
-        <v>4.585</v>
+        <v>3.3323</v>
       </c>
       <c r="K8" t="n">
-        <v>1.3251</v>
+        <v>1.3384</v>
       </c>
       <c r="L8" t="n">
-        <v>3.26</v>
+        <v>1.9939</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.5119</v>
+        <v>-1.4283</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.0009</v>
+        <v>-1.0349</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.511</v>
+        <v>-0.3934</v>
       </c>
       <c r="P8" t="n">
-        <v>-4.6339</v>
+        <v>-2.1239</v>
       </c>
       <c r="Q8" t="n">
-        <v>-6.7577</v>
+        <v>-2.8962</v>
       </c>
       <c r="R8" t="n">
-        <v>2.1239</v>
+        <v>0.7723</v>
       </c>
       <c r="S8" t="n">
-        <v>1.8535</v>
+        <v>0.993</v>
       </c>
       <c r="T8" t="n">
-        <v>1.7096</v>
+        <v>0.8135</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1439</v>
+        <v>0.1795</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.3282</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.3282</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.1085</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.8176</v>
+        <v>-1.4452</v>
       </c>
       <c r="F9" t="n">
-        <v>1.7091</v>
+        <v>2.1312</v>
       </c>
       <c r="G9" t="n">
         <v>1.8364</v>
@@ -1156,13 +1156,13 @@
         <v>1.5446</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0221</v>
+        <v>0.7724</v>
       </c>
       <c r="T9" t="n">
-        <v>0.2204</v>
+        <v>0.5928</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2425</v>
+        <v>0.1796</v>
       </c>
       <c r="V9" t="n">
         <v>-0.5712</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>G. PEREZ HERNANDEZ</t>
+          <t>A. AMON BYSTROVA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.1317</v>
+        <v>0.5513</v>
       </c>
       <c r="E10" t="n">
-        <v>0.5187</v>
+        <v>0.2625</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.6504</v>
+        <v>0.2888</v>
       </c>
       <c r="G10" t="n">
-        <v>1.904</v>
+        <v>-1.3963</v>
       </c>
       <c r="H10" t="n">
-        <v>0.3034</v>
+        <v>-1.351</v>
       </c>
       <c r="I10" t="n">
-        <v>1.6005</v>
+        <v>-0.0453</v>
       </c>
       <c r="J10" t="n">
-        <v>3.3323</v>
+        <v>0.0254</v>
       </c>
       <c r="K10" t="n">
-        <v>1.3384</v>
+        <v>-0.178</v>
       </c>
       <c r="L10" t="n">
-        <v>1.9939</v>
+        <v>0.2035</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.4283</v>
+        <v>-1.4217</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.0349</v>
+        <v>-1.173</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.3934</v>
+        <v>-0.2487</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.1239</v>
+        <v>-1.5446</v>
       </c>
       <c r="Q10" t="n">
         <v>-2.8962</v>
       </c>
       <c r="R10" t="n">
-        <v>0.7723</v>
+        <v>1.3515</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0882</v>
+        <v>2.5927</v>
       </c>
       <c r="T10" t="n">
-        <v>0.08260000000000001</v>
+        <v>2.2337</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0056</v>
+        <v>0.359</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.8995</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.8995</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.4414</v>
+        <v>-2.0566</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.2355</v>
+        <v>-1.9252</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.2059</v>
+        <v>-0.1314</v>
       </c>
       <c r="G11" t="n">
         <v>-1.0016</v>
@@ -1312,13 +1312,13 @@
         <v>0.3862</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1048</v>
+        <v>0.4896</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2206</v>
+        <v>0.5309</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1158</v>
+        <v>-0.0413</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.905</v>
+        <v>-3.3865</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.5101</v>
+        <v>-1.0412</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.3949</v>
+        <v>-2.3453</v>
       </c>
       <c r="G12" t="n">
         <v>-2.6828</v>
@@ -1390,13 +1390,13 @@
         <v>0.5792</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.5738</v>
+        <v>-0.0552</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1932</v>
+        <v>0.2757</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3806</v>
+        <v>-0.3309</v>
       </c>
       <c r="V12" t="n">
         <v>-1.2277</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>18.2994</v>
+        <v>19.679</v>
       </c>
       <c r="E13" t="n">
-        <v>9.643300000000002</v>
+        <v>11.023</v>
       </c>
       <c r="F13" t="n">
-        <v>8.655900000000001</v>
+        <v>8.655900000000003</v>
       </c>
       <c r="G13" t="n">
         <v>12.5867</v>
@@ -1450,7 +1450,7 @@
         <v>14.7626</v>
       </c>
       <c r="M13" t="n">
-        <v>-6.3214</v>
+        <v>-6.321400000000001</v>
       </c>
       <c r="N13" t="n">
         <v>-5.8686</v>
@@ -1459,7 +1459,7 @@
         <v>-0.4526</v>
       </c>
       <c r="P13" t="n">
-        <v>-9.653999999999996</v>
+        <v>-9.654</v>
       </c>
       <c r="Q13" t="n">
         <v>-24.1349</v>
@@ -1468,13 +1468,13 @@
         <v>14.4808</v>
       </c>
       <c r="S13" t="n">
-        <v>13.2396</v>
+        <v>14.6192</v>
       </c>
       <c r="T13" t="n">
-        <v>11.0293</v>
+        <v>12.4089</v>
       </c>
       <c r="U13" t="n">
-        <v>2.2101</v>
+        <v>2.2104</v>
       </c>
       <c r="V13" t="n">
         <v>2.1272</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.5589</v>
+        <v>3.5741</v>
       </c>
       <c r="E14" t="n">
-        <v>3.3691</v>
+        <v>3.0588</v>
       </c>
       <c r="F14" t="n">
-        <v>0.1898</v>
+        <v>0.5152</v>
       </c>
       <c r="G14" t="n">
         <v>2.0035</v>
@@ -1546,13 +1546,13 @@
         <v>1.9308</v>
       </c>
       <c r="S14" t="n">
-        <v>0.033</v>
+        <v>0.0482</v>
       </c>
       <c r="T14" t="n">
-        <v>0.6894</v>
+        <v>0.3791</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.6564</v>
+        <v>-0.3309</v>
       </c>
       <c r="V14" t="n">
         <v>-0.4084</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.869</v>
+        <v>3.4702</v>
       </c>
       <c r="E15" t="n">
         <v>5.6936</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.8247</v>
+        <v>-2.2234</v>
       </c>
       <c r="G15" t="n">
         <v>5.0994</v>
@@ -1624,13 +1624,13 @@
         <v>2.51</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.822</v>
+        <v>-0.2208</v>
       </c>
       <c r="T15" t="n">
         <v>0.1651</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.9871</v>
+        <v>-0.3859</v>
       </c>
       <c r="V15" t="n">
         <v>-1.0222</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.1027</v>
+        <v>2.89</v>
       </c>
       <c r="E16" t="n">
-        <v>0.4343</v>
+        <v>0.7446</v>
       </c>
       <c r="F16" t="n">
-        <v>1.6683</v>
+        <v>2.1454</v>
       </c>
       <c r="G16" t="n">
         <v>2.661</v>
@@ -1702,13 +1702,13 @@
         <v>2.1239</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.5941</v>
+        <v>-0.8067</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.4966</v>
+        <v>-0.1864</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.0974</v>
+        <v>-0.6203</v>
       </c>
       <c r="V16" t="n">
         <v>-0.1228</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6084000000000001</v>
+        <v>0.3767</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.5787</v>
+        <v>-0.7855</v>
       </c>
       <c r="F17" t="n">
-        <v>1.187</v>
+        <v>1.1622</v>
       </c>
       <c r="G17" t="n">
         <v>-1.2345</v>
@@ -1780,13 +1780,13 @@
         <v>0.5792</v>
       </c>
       <c r="S17" t="n">
-        <v>0.673</v>
+        <v>0.4414</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1928</v>
+        <v>-0.014</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4802</v>
+        <v>0.4554</v>
       </c>
       <c r="V17" t="n">
         <v>1.5559</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.3315</v>
+        <v>-0.9482</v>
       </c>
       <c r="E18" t="n">
-        <v>0.02</v>
+        <v>-0.1869</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.3515</v>
+        <v>-0.7614</v>
       </c>
       <c r="G18" t="n">
         <v>-2.2983</v>
@@ -1858,13 +1858,13 @@
         <v>2.8962</v>
       </c>
       <c r="S18" t="n">
-        <v>-2.1349</v>
+        <v>-1.7516</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3866</v>
+        <v>-0.5935</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.7483</v>
+        <v>-1.1581</v>
       </c>
       <c r="V18" t="n">
         <v>0.2055</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. DIAZ CARBALLO</t>
+          <t>G. GARRIDO GUERREIRO DE SOUSA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.2985</v>
+        <v>-1.9477</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.0632</v>
+        <v>-1.7625</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7647</v>
+        <v>-0.1852</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.7179</v>
+        <v>-4.5775</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.4691</v>
+        <v>-0.0834</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.2487</v>
+        <v>-4.4942</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.1927</v>
+        <v>-1.6794</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.1927</v>
+        <v>0.2624</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>-1.9418</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.5251</v>
+        <v>-2.8981</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.2764</v>
+        <v>-0.3458</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.2487</v>
+        <v>-2.5524</v>
       </c>
       <c r="P19" t="n">
-        <v>1.3515</v>
+        <v>3.0892</v>
       </c>
       <c r="Q19" t="n">
         <v>-0.9654</v>
       </c>
       <c r="R19" t="n">
-        <v>2.3169</v>
+        <v>4.0546</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.1529</v>
+        <v>-0.9931</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2486</v>
+        <v>-0.3453</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.9043</v>
+        <v>-0.6477000000000001</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.7792</v>
+        <v>0.5337</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.6565</v>
+        <v>1.2277</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.1228</v>
+        <v>-0.694</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>E. BUENO KNUTSEN</t>
+          <t>A. DIAZ CARBALLO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.7528</v>
+        <v>-2.3937</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.9883</v>
+        <v>-3.3735</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.7645</v>
+        <v>0.9798</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.7473</v>
+        <v>-1.7179</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.5447</v>
+        <v>-1.4691</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.2027</v>
+        <v>-0.2487</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.933</v>
+        <v>-1.1927</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.4063</v>
+        <v>-1.1927</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.5266999999999999</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.8143</v>
+        <v>-0.5251</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.1384</v>
+        <v>-0.2764</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.6758999999999999</v>
+        <v>-0.2487</v>
       </c>
       <c r="P20" t="n">
-        <v>0.9654</v>
+        <v>1.3515</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-0.9654</v>
       </c>
       <c r="R20" t="n">
-        <v>0.9654</v>
+        <v>2.3169</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.9709</v>
+        <v>-1.2481</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0553</v>
+        <v>-0.5589</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.9156</v>
+        <v>-0.6892</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-0.7792</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>-0.6565</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.1228</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>G. GARRIDO GUERREIRO DE SOUSA</t>
+          <t>E. BUENO KNUTSEN</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.1446</v>
+        <v>-2.4715</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.383</v>
+        <v>-1.7815</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.7616000000000001</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="G21" t="n">
-        <v>-4.5775</v>
+        <v>-2.7473</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.0834</v>
+        <v>-1.5447</v>
       </c>
       <c r="I21" t="n">
-        <v>-4.4942</v>
+        <v>-1.2027</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.6794</v>
+        <v>-1.933</v>
       </c>
       <c r="K21" t="n">
-        <v>0.2624</v>
+        <v>-1.4063</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.9418</v>
+        <v>-0.5266999999999999</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.8981</v>
+        <v>-0.8143</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.3458</v>
+        <v>-0.1384</v>
       </c>
       <c r="O21" t="n">
-        <v>-2.5524</v>
+        <v>-0.6758999999999999</v>
       </c>
       <c r="P21" t="n">
-        <v>3.0892</v>
+        <v>0.9654</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9654</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>4.0546</v>
+        <v>0.9654</v>
       </c>
       <c r="S21" t="n">
-        <v>-2.19</v>
+        <v>-0.6896</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.9659</v>
+        <v>0.1515</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.2242</v>
+        <v>-0.8411</v>
       </c>
       <c r="V21" t="n">
-        <v>0.5337</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.2277</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.694</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.2035</v>
+        <v>-3.3221</v>
       </c>
       <c r="E22" t="n">
-        <v>0.2757</v>
+        <v>0.0689</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.4792</v>
+        <v>-3.391</v>
       </c>
       <c r="G22" t="n">
         <v>-0.9028</v>
@@ -2170,13 +2170,13 @@
         <v>0.7723</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.9433</v>
+        <v>-1.0619</v>
       </c>
       <c r="T22" t="n">
-        <v>0.1377</v>
+        <v>-0.0692</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.081</v>
+        <v>-0.9927</v>
       </c>
       <c r="V22" t="n">
         <v>-2.1297</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.0294</v>
+        <v>-5.1219</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.9908</v>
+        <v>-4.784</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.0385</v>
+        <v>-0.338</v>
       </c>
       <c r="G23" t="n">
         <v>-1.6068</v>
@@ -2248,13 +2248,13 @@
         <v>2.8962</v>
       </c>
       <c r="S23" t="n">
-        <v>-2.6313</v>
+        <v>-1.7239</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.9657</v>
+        <v>-0.7589</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.6656</v>
+        <v>-0.965</v>
       </c>
       <c r="V23" t="n">
         <v>1.1049</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-8.677899999999999</v>
+        <v>-8.2684</v>
       </c>
       <c r="E24" t="n">
-        <v>-5.4447</v>
+        <v>-5.5481</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.2332</v>
+        <v>-2.7202</v>
       </c>
       <c r="G24" t="n">
         <v>-7.2654</v>
@@ -2326,13 +2326,13 @@
         <v>3.0892</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.5062</v>
+        <v>-1.0966</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.2764</v>
+        <v>-0.3798</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.2298</v>
+        <v>-0.7168</v>
       </c>
       <c r="V24" t="n">
         <v>-1.0648</v>
@@ -2359,19 +2359,19 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-18.2992</v>
+        <v>-14.1625</v>
       </c>
       <c r="E25" t="n">
-        <v>-8.656000000000001</v>
+        <v>-8.6561</v>
       </c>
       <c r="F25" t="n">
-        <v>-9.6434</v>
+        <v>-5.506600000000001</v>
       </c>
       <c r="G25" t="n">
         <v>-12.5866</v>
       </c>
       <c r="H25" t="n">
-        <v>1.7232</v>
+        <v>1.723200000000001</v>
       </c>
       <c r="I25" t="n">
         <v>-14.3099</v>
@@ -2383,7 +2383,7 @@
         <v>5.8689</v>
       </c>
       <c r="L25" t="n">
-        <v>0.4526999999999998</v>
+        <v>0.4526999999999993</v>
       </c>
       <c r="M25" t="n">
         <v>-18.908</v>
@@ -2395,7 +2395,7 @@
         <v>-14.7626</v>
       </c>
       <c r="P25" t="n">
-        <v>9.653799999999999</v>
+        <v>9.6538</v>
       </c>
       <c r="Q25" t="n">
         <v>-14.4809</v>
@@ -2404,13 +2404,13 @@
         <v>24.1347</v>
       </c>
       <c r="S25" t="n">
-        <v>-13.2396</v>
+        <v>-9.1027</v>
       </c>
       <c r="T25" t="n">
-        <v>-2.2101</v>
+        <v>-2.2103</v>
       </c>
       <c r="U25" t="n">
-        <v>-11.0295</v>
+        <v>-6.892300000000001</v>
       </c>
       <c r="V25" t="n">
         <v>-2.1271</v>
